--- a/data/reports/Загрузка_гейтов_2026-06-23.xlsx
+++ b/data/reports/Загрузка_гейтов_2026-06-23.xlsx
@@ -1138,13 +1138,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I8" s="15" t="n">
         <v>0.09</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>0.08</v>
@@ -1603,13 +1603,13 @@
         <v>0.04</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I23" s="15" t="n">
         <v>0.04</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K23" s="15" t="n">
         <v>0.04</v>
@@ -7321,7 +7321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K114"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7653,10 +7653,10 @@
         <v>0.02</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>9</v>
@@ -7665,7 +7665,7 @@
         <v>0.04</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K13" s="15" t="n">
         <v>0.03</v>
@@ -7718,7 +7718,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>12</v>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="E20" s="18" t="n"/>
       <c r="F20" s="7" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G20" s="18" t="n"/>
       <c r="H20" s="7" t="n">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="I20" s="18" t="n"/>
       <c r="J20" s="7" t="n">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="K20" s="18" t="n"/>
     </row>
@@ -7950,7 +7950,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>1</v>
@@ -7962,7 +7962,7 @@
         <v>6</v>
       </c>
       <c r="K24" s="15" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="25">
@@ -8016,7 +8016,7 @@
         <v>6</v>
       </c>
       <c r="K26" s="15" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="27">
@@ -8035,7 +8035,7 @@
         <v>2</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>4</v>
@@ -8078,13 +8078,13 @@
         <v>4</v>
       </c>
       <c r="K28" s="15" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="29">
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="D29" s="5" t="n"/>
@@ -8107,63 +8107,63 @@
     <row r="30">
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="15" t="n"/>
-      <c r="F30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="15" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>0.16</v>
+      </c>
       <c r="J30" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="15" t="n"/>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.06</v>
+      </c>
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="15" t="n"/>
-      <c r="H31" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>0.16</v>
-      </c>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="15" t="n"/>
       <c r="J31" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K31" s="15" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="32">
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="15" t="n"/>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>0.08</v>
+      </c>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="15" t="n"/>
       <c r="J32" s="5" t="n">
@@ -8176,30 +8176,38 @@
     <row r="33">
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="15" t="n"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0.06</v>
+      </c>
       <c r="F33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="15" t="n"/>
+        <v>0.17</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>0.05</v>
+      </c>
       <c r="J33" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="34">
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -8209,362 +8217,362 @@
         <v>0.06</v>
       </c>
       <c r="F34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G34" s="15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="K34" s="15" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" s="15" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="n"/>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="A35" s="16" t="n"/>
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>ИТОГО зоны</t>
         </is>
       </c>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="7" t="n">
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="E36" s="18" t="n"/>
-      <c r="F36" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="G36" s="18" t="n"/>
-      <c r="H36" s="7" t="n">
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="I36" s="18" t="n"/>
-      <c r="J36" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="K36" s="18" t="n"/>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="K35" s="18" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>Терм. D</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>Внутренние (ВВЛ)</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="14" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>Терм. D</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>Внутренние (ВВЛ)</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="14" t="n"/>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="14" t="n"/>
-      <c r="G38" s="14" t="n"/>
-      <c r="H38" s="14" t="n"/>
-      <c r="I38" s="14" t="n"/>
-      <c r="J38" s="14" t="n"/>
-      <c r="K38" s="14" t="n"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" s="15" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="39">
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="K39" s="15" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="40">
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I40" s="15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="K40" s="15" t="n">
         <v>0.14</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="K40" s="15" t="n">
-        <v>0.13</v>
       </c>
     </row>
     <row r="41">
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E41" s="15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G41" s="15" t="n">
         <v>0.15</v>
       </c>
-      <c r="F41" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G41" s="15" t="n">
+      <c r="H41" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="K41" s="15" t="n">
         <v>0.13</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J41" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="K41" s="15" t="n">
-        <v>0.14</v>
       </c>
     </row>
     <row r="42">
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="K42" s="15" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="43">
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G43" s="15" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H43" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E43" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G43" s="15" t="n">
+      <c r="I43" s="15" t="n">
         <v>0.06</v>
       </c>
-      <c r="H43" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="J43" s="5" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="K43" s="15" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="44">
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>0.16</v>
+        <v>0.04</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="K44" s="15" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F45" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="E45" s="15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="G45" s="15" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K45" s="15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E46" s="15" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I46" s="15" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K46" s="15" t="n">
         <v>0.08</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="K46" s="15" t="n">
-        <v>0.1</v>
       </c>
     </row>
     <row r="47">
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H47" s="5" t="n">
         <v>15</v>
@@ -8573,166 +8581,162 @@
         <v>0.13</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="48">
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E48" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G48" s="15" t="n">
         <v>0.08</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="H48" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G48" s="15" t="n">
+      <c r="I48" s="15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H48" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>0.13</v>
-      </c>
       <c r="J48" s="5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G49" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="K49" s="15" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="16" t="n"/>
-      <c r="B50" s="17" t="inlineStr">
+      <c r="A49" s="16" t="n"/>
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>ИТОГО зоны</t>
         </is>
       </c>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="7" t="n">
+      <c r="C49" s="16" t="n"/>
+      <c r="D49" s="7" t="n">
         <v>131</v>
       </c>
-      <c r="E50" s="18" t="n"/>
-      <c r="F50" s="7" t="n">
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="7" t="n">
         <v>113</v>
       </c>
-      <c r="G50" s="18" t="n"/>
-      <c r="H50" s="7" t="n">
+      <c r="G49" s="18" t="n"/>
+      <c r="H49" s="7" t="n">
         <v>118</v>
       </c>
-      <c r="I50" s="18" t="n"/>
-      <c r="J50" s="7" t="n">
+      <c r="I49" s="18" t="n"/>
+      <c r="J49" s="7" t="n">
         <v>362</v>
       </c>
-      <c r="K50" s="18" t="n"/>
+      <c r="K49" s="18" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>Терм. D</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>Не классиф.</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="n"/>
+      <c r="D51" s="14" t="n"/>
+      <c r="E51" s="14" t="n"/>
+      <c r="F51" s="14" t="n"/>
+      <c r="G51" s="14" t="n"/>
+      <c r="H51" s="14" t="n"/>
+      <c r="I51" s="14" t="n"/>
+      <c r="J51" s="14" t="n"/>
+      <c r="K51" s="14" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>Терм. D</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>Не классиф.</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="n"/>
-      <c r="D52" s="14" t="n"/>
-      <c r="E52" s="14" t="n"/>
-      <c r="F52" s="14" t="n"/>
-      <c r="G52" s="14" t="n"/>
-      <c r="H52" s="14" t="n"/>
-      <c r="I52" s="14" t="n"/>
-      <c r="J52" s="14" t="n"/>
-      <c r="K52" s="14" t="n"/>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="15" t="n"/>
+      <c r="F52" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" s="15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="15" t="n"/>
+      <c r="J52" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K52" s="15" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="53">
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>D11</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="15" t="n"/>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>0.08</v>
+      </c>
       <c r="F53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="15" t="n"/>
+        <v>0.25</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>0.08</v>
+      </c>
       <c r="J53" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="54">
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F54" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="15" t="n"/>
+      <c r="H54" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G54" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="I54" s="15" t="n">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="J54" s="5" t="n">
         <v>5</v>
@@ -8744,34 +8748,38 @@
     <row r="55">
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="15" t="n"/>
+        <v>0.08</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="15" t="n">
+        <v>0.08</v>
+      </c>
       <c r="H55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J55" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I55" s="15" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="K55" s="15" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="56">
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
@@ -8781,10 +8789,10 @@
         <v>0.08</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="H56" s="5" t="n">
         <v>1</v>
@@ -8793,23 +8801,23 @@
         <v>0.08</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K56" s="15" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="57">
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="F57" s="5" t="n">
         <v>2</v>
@@ -8818,36 +8826,32 @@
         <v>0.17</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="58">
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" s="15" t="n">
-        <v>0.17</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="15" t="n"/>
       <c r="H58" s="5" t="n">
         <v>2</v>
       </c>
@@ -8855,31 +8859,31 @@
         <v>0.15</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K58" s="15" t="n">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="59">
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="F59" s="5" t="n"/>
       <c r="G59" s="15" t="n"/>
       <c r="H59" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="J59" s="5" t="n">
         <v>3</v>
@@ -8891,138 +8895,134 @@
     <row r="60">
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F60" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E60" s="15" t="n">
+      <c r="G60" s="15" t="n">
         <v>0.17</v>
       </c>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="15" t="n"/>
       <c r="H60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="61">
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F61" s="5" t="n">
+      <c r="A61" s="16" t="n"/>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>ИТОГО зоны</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="n"/>
+      <c r="D61" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E61" s="18" t="n"/>
+      <c r="F61" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G61" s="18" t="n"/>
+      <c r="H61" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="I61" s="18" t="n"/>
+      <c r="J61" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="K61" s="18" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>Терм. E</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>Внутренние (ВВЛ)</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="n"/>
+      <c r="D63" s="14" t="n"/>
+      <c r="E63" s="14" t="n"/>
+      <c r="F63" s="14" t="n"/>
+      <c r="G63" s="14" t="n"/>
+      <c r="H63" s="14" t="n"/>
+      <c r="I63" s="14" t="n"/>
+      <c r="J63" s="14" t="n"/>
+      <c r="K63" s="14" t="n"/>
+    </row>
+    <row r="64">
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="15" t="n"/>
+      <c r="H64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G61" s="15" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I61" s="15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J61" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K61" s="15" t="n">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="16" t="n"/>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>ИТОГО зоны</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="n"/>
-      <c r="D62" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="E62" s="18" t="n"/>
-      <c r="F62" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="G62" s="18" t="n"/>
-      <c r="H62" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="I62" s="18" t="n"/>
-      <c r="J62" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="K62" s="18" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>Терм. E</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>Внутренние (ВВЛ)</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n"/>
-      <c r="D64" s="14" t="n"/>
-      <c r="E64" s="14" t="n"/>
-      <c r="F64" s="14" t="n"/>
-      <c r="G64" s="14" t="n"/>
-      <c r="H64" s="14" t="n"/>
-      <c r="I64" s="14" t="n"/>
-      <c r="J64" s="14" t="n"/>
-      <c r="K64" s="14" t="n"/>
+      <c r="K64" s="15" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="65">
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>E10</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="15" t="n"/>
-      <c r="H65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I65" s="15" t="n">
-        <v>1</v>
-      </c>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="15" t="n"/>
+      <c r="F65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="15" t="n"/>
       <c r="J65" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K65" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="66">
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D66" s="5" t="n"/>
@@ -9043,194 +9043,202 @@
       </c>
     </row>
     <row r="67">
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>E7</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="15" t="n"/>
-      <c r="F67" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H67" s="5" t="n"/>
-      <c r="I67" s="15" t="n"/>
-      <c r="J67" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K67" s="15" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="16" t="n"/>
-      <c r="B68" s="17" t="inlineStr">
+      <c r="A67" s="16" t="n"/>
+      <c r="B67" s="17" t="inlineStr">
         <is>
           <t>ИТОГО зоны</t>
         </is>
       </c>
-      <c r="C68" s="16" t="n"/>
-      <c r="D68" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="18" t="n"/>
-      <c r="F68" s="7" t="n">
+      <c r="C67" s="16" t="n"/>
+      <c r="D67" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G68" s="18" t="n"/>
-      <c r="H68" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I68" s="18" t="n"/>
-      <c r="J68" s="7" t="n">
+      <c r="G67" s="18" t="n"/>
+      <c r="H67" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="18" t="n"/>
+      <c r="J67" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="K68" s="18" t="n"/>
+      <c r="K67" s="18" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>Терм. E</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>Международные (МВЛ)</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="n"/>
+      <c r="D69" s="14" t="n"/>
+      <c r="E69" s="14" t="n"/>
+      <c r="F69" s="14" t="n"/>
+      <c r="G69" s="14" t="n"/>
+      <c r="H69" s="14" t="n"/>
+      <c r="I69" s="14" t="n"/>
+      <c r="J69" s="14" t="n"/>
+      <c r="K69" s="14" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="13" t="inlineStr">
-        <is>
-          <t>Терм. E</t>
-        </is>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>Международные (МВЛ)</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="n"/>
-      <c r="D70" s="14" t="n"/>
-      <c r="E70" s="14" t="n"/>
-      <c r="F70" s="14" t="n"/>
-      <c r="G70" s="14" t="n"/>
-      <c r="H70" s="14" t="n"/>
-      <c r="I70" s="14" t="n"/>
-      <c r="J70" s="14" t="n"/>
-      <c r="K70" s="14" t="n"/>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G70" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K70" s="15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="71">
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>E10</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E71" s="15" t="n">
-        <v>0.1</v>
-      </c>
+          <t>E12</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="15" t="n"/>
       <c r="F71" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G71" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I71" s="15" t="n">
-        <v>0.04</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="15" t="n"/>
       <c r="J71" s="5" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="K71" s="15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="72">
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="15" t="n"/>
+          <t>E13</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.06</v>
+      </c>
       <c r="F72" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H72" s="5" t="n"/>
-      <c r="I72" s="15" t="n"/>
+        <v>0.04</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>0.05</v>
+      </c>
       <c r="J72" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="73">
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E14</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="K73" s="15" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="74">
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>E14</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E74" s="15" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G74" s="15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F74" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G74" s="15" t="n">
-        <v>0.08</v>
-      </c>
       <c r="H74" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="75">
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
@@ -9240,35 +9248,35 @@
         <v>0.04</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G75" s="15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K75" s="15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="76">
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>6</v>
@@ -9277,10 +9285,10 @@
         <v>0.04</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="J76" s="5" t="n">
         <v>17</v>
@@ -9292,51 +9300,51 @@
     <row r="77">
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>E19</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K77" s="15" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="78">
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E20</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E78" s="15" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G78" s="15" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H78" s="5" t="n">
         <v>4</v>
@@ -9345,213 +9353,213 @@
         <v>0.03</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="79">
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>E20</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E79" s="15" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="G79" s="15" t="n">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="I79" s="15" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="K79" s="15" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="80">
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E80" s="15" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G80" s="15" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I80" s="15" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="81">
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>E4</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="G81" s="15" t="n">
-        <v>0.13</v>
-      </c>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="15" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="15" t="n"/>
       <c r="H81" s="5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I81" s="15" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="K81" s="15" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>E5</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="n"/>
-      <c r="E82" s="15" t="n"/>
-      <c r="F82" s="5" t="n"/>
-      <c r="G82" s="15" t="n"/>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G82" s="15" t="n">
+        <v>0.14</v>
+      </c>
       <c r="H82" s="5" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I82" s="15" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="K82" s="15" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="83">
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>0.14</v>
+        <v>0.04</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G83" s="15" t="n">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="K83" s="15" t="n">
-        <v>0.14</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="84">
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E8</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G84" s="15" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I84" s="15" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>E8</t>
+          <t>E9</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G85" s="15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I85" s="15" t="n">
         <v>0.06</v>
-      </c>
-      <c r="H85" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I85" s="15" t="n">
-        <v>0.08</v>
       </c>
       <c r="J85" s="5" t="n">
         <v>31</v>
@@ -9561,86 +9569,82 @@
       </c>
     </row>
     <row r="86">
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>E9</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E86" s="15" t="n">
+      <c r="A86" s="16" t="n"/>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>ИТОГО зоны</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="n"/>
+      <c r="D86" s="7" t="n">
+        <v>159</v>
+      </c>
+      <c r="E86" s="18" t="n"/>
+      <c r="F86" s="7" t="n">
+        <v>138</v>
+      </c>
+      <c r="G86" s="18" t="n"/>
+      <c r="H86" s="7" t="n">
+        <v>149</v>
+      </c>
+      <c r="I86" s="18" t="n"/>
+      <c r="J86" s="7" t="n">
+        <v>446</v>
+      </c>
+      <c r="K86" s="18" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>Терм. E</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>Не классиф.</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="n"/>
+      <c r="D88" s="14" t="n"/>
+      <c r="E88" s="14" t="n"/>
+      <c r="F88" s="14" t="n"/>
+      <c r="G88" s="14" t="n"/>
+      <c r="H88" s="14" t="n"/>
+      <c r="I88" s="14" t="n"/>
+      <c r="J88" s="14" t="n"/>
+      <c r="K88" s="14" t="n"/>
+    </row>
+    <row r="89">
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="15" t="n"/>
+      <c r="F89" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" s="15" t="n">
         <v>0.06</v>
       </c>
-      <c r="F86" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="G86" s="15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H86" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I86" s="15" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J86" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="K86" s="15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="16" t="n"/>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>ИТОГО зоны</t>
-        </is>
-      </c>
-      <c r="C87" s="16" t="n"/>
-      <c r="D87" s="7" t="n">
-        <v>159</v>
-      </c>
-      <c r="E87" s="18" t="n"/>
-      <c r="F87" s="7" t="n">
-        <v>138</v>
-      </c>
-      <c r="G87" s="18" t="n"/>
-      <c r="H87" s="7" t="n">
-        <v>149</v>
-      </c>
-      <c r="I87" s="18" t="n"/>
-      <c r="J87" s="7" t="n">
-        <v>446</v>
-      </c>
-      <c r="K87" s="18" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="13" t="inlineStr">
-        <is>
-          <t>Терм. E</t>
-        </is>
-      </c>
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>Не классиф.</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="n"/>
-      <c r="D89" s="14" t="n"/>
-      <c r="E89" s="14" t="n"/>
-      <c r="F89" s="14" t="n"/>
-      <c r="G89" s="14" t="n"/>
-      <c r="H89" s="14" t="n"/>
-      <c r="I89" s="14" t="n"/>
-      <c r="J89" s="14" t="n"/>
-      <c r="K89" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="D90" s="5" t="n"/>
@@ -9652,87 +9656,87 @@
         <v>0.11</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I90" s="15" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="91">
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>E13</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="n"/>
-      <c r="E91" s="15" t="n"/>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0.33</v>
+      </c>
       <c r="F91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G91" s="15" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I91" s="15" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K91" s="15" t="n">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="92">
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E92" s="15" t="n">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G92" s="15" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I92" s="15" t="n">
-        <v>0.33</v>
-      </c>
+        <v>0.11</v>
+      </c>
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="15" t="n"/>
       <c r="J92" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>0.3</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="93">
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" s="15" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="F93" s="5" t="n">
         <v>1</v>
@@ -9743,49 +9747,49 @@
       <c r="H93" s="5" t="n"/>
       <c r="I93" s="15" t="n"/>
       <c r="J93" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K93" s="15" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="94">
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>E18</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" s="15" t="n">
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="n"/>
+      <c r="E94" s="15" t="n"/>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="15" t="n"/>
+      <c r="H94" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="15" t="n">
         <v>0.08</v>
       </c>
-      <c r="F94" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="15" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H94" s="5" t="n"/>
-      <c r="I94" s="15" t="n"/>
       <c r="J94" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="95">
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>E19</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="D95" s="5" t="n"/>
       <c r="E95" s="15" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="15" t="n"/>
+      <c r="F95" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="15" t="n">
+        <v>0.11</v>
+      </c>
       <c r="H95" s="5" t="n">
         <v>1</v>
       </c>
@@ -9793,417 +9797,390 @@
         <v>0.08</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K95" s="15" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="96">
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>E3</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="n"/>
-      <c r="E96" s="15" t="n"/>
-      <c r="F96" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" s="15" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I96" s="15" t="n">
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="15" t="n">
         <v>0.08</v>
       </c>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="15" t="n"/>
+      <c r="H96" s="5" t="n"/>
+      <c r="I96" s="15" t="n"/>
       <c r="J96" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="97">
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>E4</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="15" t="n">
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="15" t="n"/>
+      <c r="F97" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G97" s="15" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="15" t="n">
         <v>0.08</v>
       </c>
-      <c r="F97" s="5" t="n"/>
-      <c r="G97" s="15" t="n"/>
-      <c r="H97" s="5" t="n"/>
-      <c r="I97" s="15" t="n"/>
       <c r="J97" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K97" s="15" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="98">
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>E6</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="n"/>
-      <c r="E98" s="15" t="n"/>
-      <c r="F98" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G98" s="15" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H98" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I98" s="15" t="n">
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="15" t="n">
         <v>0.08</v>
       </c>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="15" t="n"/>
+      <c r="H98" s="5" t="n"/>
+      <c r="I98" s="15" t="n"/>
       <c r="J98" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="99">
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E8</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" s="15" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="F99" s="5" t="n"/>
       <c r="G99" s="15" t="n"/>
-      <c r="H99" s="5" t="n"/>
-      <c r="I99" s="15" t="n"/>
+      <c r="H99" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I99" s="15" t="n">
+        <v>0.17</v>
+      </c>
       <c r="J99" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K99" s="15" t="n">
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="100">
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>E8</t>
+          <t>E9</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="15" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="F100" s="5" t="n"/>
       <c r="G100" s="15" t="n"/>
-      <c r="H100" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I100" s="15" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="H100" s="5" t="n"/>
+      <c r="I100" s="15" t="n"/>
       <c r="J100" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="101">
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>E9</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F101" s="5" t="n"/>
-      <c r="G101" s="15" t="n"/>
-      <c r="H101" s="5" t="n"/>
-      <c r="I101" s="15" t="n"/>
-      <c r="J101" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K101" s="15" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="16" t="n"/>
-      <c r="B102" s="17" t="inlineStr">
+      <c r="A101" s="16" t="n"/>
+      <c r="B101" s="17" t="inlineStr">
         <is>
           <t>ИТОГО зоны</t>
         </is>
       </c>
-      <c r="C102" s="16" t="n"/>
-      <c r="D102" s="7" t="n">
+      <c r="C101" s="16" t="n"/>
+      <c r="D101" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="E102" s="18" t="n"/>
-      <c r="F102" s="7" t="n">
+      <c r="E101" s="18" t="n"/>
+      <c r="F101" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G102" s="18" t="n"/>
-      <c r="H102" s="7" t="n">
+      <c r="G101" s="18" t="n"/>
+      <c r="H101" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I102" s="18" t="n"/>
-      <c r="J102" s="7" t="n">
+      <c r="I101" s="18" t="n"/>
+      <c r="J101" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="K102" s="18" t="n"/>
+      <c r="K101" s="18" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="13" t="inlineStr">
+        <is>
+          <t>Терм. —</t>
+        </is>
+      </c>
+      <c r="B103" s="13" t="inlineStr">
+        <is>
+          <t>Внутренние (ВВЛ)</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="n"/>
+      <c r="D103" s="14" t="n"/>
+      <c r="E103" s="14" t="n"/>
+      <c r="F103" s="14" t="n"/>
+      <c r="G103" s="14" t="n"/>
+      <c r="H103" s="14" t="n"/>
+      <c r="I103" s="14" t="n"/>
+      <c r="J103" s="14" t="n"/>
+      <c r="K103" s="14" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="13" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G104" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I104" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="K104" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="n"/>
+      <c r="B105" s="17" t="inlineStr">
+        <is>
+          <t>ИТОГО зоны</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="n"/>
+      <c r="D105" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="E105" s="18" t="n"/>
+      <c r="F105" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G105" s="18" t="n"/>
+      <c r="H105" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="I105" s="18" t="n"/>
+      <c r="J105" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="K105" s="18" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="13" t="inlineStr">
         <is>
           <t>Терм. —</t>
         </is>
       </c>
-      <c r="B104" s="13" t="inlineStr">
-        <is>
-          <t>Внутренние (ВВЛ)</t>
-        </is>
-      </c>
-      <c r="C104" s="14" t="n"/>
-      <c r="D104" s="14" t="n"/>
-      <c r="E104" s="14" t="n"/>
-      <c r="F104" s="14" t="n"/>
-      <c r="G104" s="14" t="n"/>
-      <c r="H104" s="14" t="n"/>
-      <c r="I104" s="14" t="n"/>
-      <c r="J104" s="14" t="n"/>
-      <c r="K104" s="14" t="n"/>
-    </row>
-    <row r="105">
-      <c r="C105" s="5" t="inlineStr">
+      <c r="B107" s="13" t="inlineStr">
+        <is>
+          <t>Международные (МВЛ)</t>
+        </is>
+      </c>
+      <c r="C107" s="14" t="n"/>
+      <c r="D107" s="14" t="n"/>
+      <c r="E107" s="14" t="n"/>
+      <c r="F107" s="14" t="n"/>
+      <c r="G107" s="14" t="n"/>
+      <c r="H107" s="14" t="n"/>
+      <c r="I107" s="14" t="n"/>
+      <c r="J107" s="14" t="n"/>
+      <c r="K107" s="14" t="n"/>
+    </row>
+    <row r="108">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D105" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="E105" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G105" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H105" s="5" t="n">
+      <c r="D108" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I105" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="K105" s="15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="16" t="n"/>
-      <c r="B106" s="17" t="inlineStr">
+      <c r="I108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="K108" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="16" t="n"/>
+      <c r="B109" s="17" t="inlineStr">
         <is>
           <t>ИТОГО зоны</t>
         </is>
       </c>
-      <c r="C106" s="16" t="n"/>
-      <c r="D106" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="E106" s="18" t="n"/>
-      <c r="F106" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="G106" s="18" t="n"/>
-      <c r="H106" s="7" t="n">
+      <c r="C109" s="16" t="n"/>
+      <c r="D109" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="E109" s="18" t="n"/>
+      <c r="F109" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G109" s="18" t="n"/>
+      <c r="H109" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="I106" s="18" t="n"/>
-      <c r="J106" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="K106" s="18" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="13" t="inlineStr">
+      <c r="I109" s="18" t="n"/>
+      <c r="J109" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="K109" s="18" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="13" t="inlineStr">
         <is>
           <t>Терм. —</t>
         </is>
       </c>
-      <c r="B108" s="13" t="inlineStr">
-        <is>
-          <t>Международные (МВЛ)</t>
-        </is>
-      </c>
-      <c r="C108" s="14" t="n"/>
-      <c r="D108" s="14" t="n"/>
-      <c r="E108" s="14" t="n"/>
-      <c r="F108" s="14" t="n"/>
-      <c r="G108" s="14" t="n"/>
-      <c r="H108" s="14" t="n"/>
-      <c r="I108" s="14" t="n"/>
-      <c r="J108" s="14" t="n"/>
-      <c r="K108" s="14" t="n"/>
-    </row>
-    <row r="109">
-      <c r="C109" s="5" t="inlineStr">
+      <c r="B111" s="13" t="inlineStr">
+        <is>
+          <t>Не классиф.</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="n"/>
+      <c r="D111" s="14" t="n"/>
+      <c r="E111" s="14" t="n"/>
+      <c r="F111" s="14" t="n"/>
+      <c r="G111" s="14" t="n"/>
+      <c r="H111" s="14" t="n"/>
+      <c r="I111" s="14" t="n"/>
+      <c r="J111" s="14" t="n"/>
+      <c r="K111" s="14" t="n"/>
+    </row>
+    <row r="112">
+      <c r="C112" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D109" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="5" t="n">
+      <c r="D112" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G112" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G109" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H109" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="I109" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="K109" s="15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="16" t="n"/>
-      <c r="B110" s="17" t="inlineStr">
+      <c r="I112" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K112" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="16" t="n"/>
+      <c r="B113" s="17" t="inlineStr">
         <is>
           <t>ИТОГО зоны</t>
         </is>
       </c>
-      <c r="C110" s="16" t="n"/>
-      <c r="D110" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="E110" s="18" t="n"/>
-      <c r="F110" s="7" t="n">
+      <c r="C113" s="16" t="n"/>
+      <c r="D113" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="18" t="n"/>
+      <c r="F113" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G113" s="18" t="n"/>
+      <c r="H113" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G110" s="18" t="n"/>
-      <c r="H110" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="I110" s="18" t="n"/>
-      <c r="J110" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="K110" s="18" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="13" t="inlineStr">
-        <is>
-          <t>Терм. —</t>
-        </is>
-      </c>
-      <c r="B112" s="13" t="inlineStr">
-        <is>
-          <t>Не классиф.</t>
-        </is>
-      </c>
-      <c r="C112" s="14" t="n"/>
-      <c r="D112" s="14" t="n"/>
-      <c r="E112" s="14" t="n"/>
-      <c r="F112" s="14" t="n"/>
-      <c r="G112" s="14" t="n"/>
-      <c r="H112" s="14" t="n"/>
-      <c r="I112" s="14" t="n"/>
-      <c r="J112" s="14" t="n"/>
-      <c r="K112" s="14" t="n"/>
-    </row>
-    <row r="113">
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G113" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I113" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="5" t="n">
+      <c r="I113" s="18" t="n"/>
+      <c r="J113" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="K113" s="15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="16" t="n"/>
-      <c r="B114" s="17" t="inlineStr">
-        <is>
-          <t>ИТОГО зоны</t>
-        </is>
-      </c>
-      <c r="C114" s="16" t="n"/>
-      <c r="D114" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" s="18" t="n"/>
-      <c r="F114" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G114" s="18" t="n"/>
-      <c r="H114" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I114" s="18" t="n"/>
-      <c r="J114" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="K114" s="18" t="n"/>
+      <c r="K113" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
